--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,14 +3277,14 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.05</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.13</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>5.85</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>17</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>5.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>17</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
         <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46041.42013888889</v>
+        <v>46041.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46041.45833333334</v>
+        <v>46041.42013888889</v>
       </c>
     </row>
     <row r="5">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46041.5</v>
+        <v>46041.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46041.53125</v>
+        <v>46041.5</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46041.54166666666</v>
+        <v>46041.53125</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46041.58333333334</v>
+        <v>46041.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46041.60416666666</v>
+        <v>46041.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>5.85</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>17</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>1.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>5.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1.95</v>
+        <v>17</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46041.625</v>
+        <v>46041.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46041.66666666666</v>
+        <v>46041.625</v>
       </c>
     </row>
     <row r="21">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46041.6875</v>
+        <v>46041.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46041.69791666666</v>
+        <v>46041.6875</v>
       </c>
     </row>
     <row r="25">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,55 +3515,55 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.95</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46041.70833333334</v>
+        <v>46041.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46041.71875</v>
+        <v>46041.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46041.79166666666</v>
+        <v>46041.71875</v>
       </c>
     </row>
     <row r="30">
@@ -3950,116 +3950,235 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>46041.79166666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3" t="n">
         <v>46041.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>5.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>17</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>5.85</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>5.85</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>17</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>1.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>5.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>17</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>5.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>17</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>5.85</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
         <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.85</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>17</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>1.13</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>5.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>17</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46041.79166666666</v>
+        <v>46041.8125</v>
       </c>
     </row>
     <row r="31">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.13</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>5.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>17</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>5.85</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.13</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.85</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>17</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.13</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>17</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>5.85</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3203,10 +3203,10 @@
         <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
         <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46041.35416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1501,40 +1501,40 @@
         <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA9" t="n">
         <v>2.08</v>
@@ -1543,22 +1543,22 @@
         <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1620,40 +1620,40 @@
         <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.81</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
         <v>2.02</v>
@@ -1662,22 +1662,22 @@
         <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1977,64 +1977,64 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2096,40 +2096,40 @@
         <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
         <v>2.3</v>
@@ -2138,22 +2138,22 @@
         <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2215,40 +2215,40 @@
         <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.92</v>
@@ -2257,22 +2257,22 @@
         <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2334,40 +2334,40 @@
         <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
         <v>2.07</v>
@@ -2376,22 +2376,22 @@
         <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2453,40 +2453,40 @@
         <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
         <v>2.12</v>
@@ -2495,22 +2495,22 @@
         <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2572,40 +2572,40 @@
         <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA18" t="n">
         <v>2.1</v>
@@ -2614,22 +2614,22 @@
         <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AF26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46041.71875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.75</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>8</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.53</v>
+        <v>1.84</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>3.04</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.89</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.84</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.05</v>
+        <v>7.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>3.24</v>
@@ -2126,16 +2126,16 @@
         <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
         <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
         <v>4.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,67 +2325,67 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.36</v>
+        <v>4.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="T16" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>4.31</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
         <v>1.29</v>
@@ -2459,7 +2459,7 @@
         <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="R17" t="n">
         <v>1.46</v>
@@ -2468,13 +2468,13 @@
         <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
         <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
@@ -2483,7 +2483,7 @@
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
         <v>2.8</v>
@@ -2510,7 +2510,7 @@
         <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>2.43</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.39</v>
+        <v>3.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>3.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.43</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="O26" t="n">
         <v>3.25</v>
@@ -3545,7 +3545,7 @@
         <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
@@ -3560,10 +3560,10 @@
         <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>4.6</v>
@@ -3575,7 +3575,7 @@
         <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
         <v>1.4</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.05</v>
+        <v>7.81</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.81</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
         <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
@@ -2001,40 +2001,40 @@
         <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.24</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>3.24</v>
       </c>
       <c r="P15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.36</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.88</v>
+        <v>4.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
         <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.58</v>
+        <v>4.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T19" t="n">
         <v>3.2</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.09</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.41</v>
+        <v>4.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>3.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.43</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>2.43</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.39</v>
+        <v>3.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>3.17</v>
       </c>
       <c r="O27" t="n">
-        <v>2.39</v>
+        <v>3.06</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>4.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.25</v>
+        <v>2.98</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.14</v>
+        <v>0.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>0.23</v>
       </c>
       <c r="N28" t="n">
-        <v>3.17</v>
+        <v>0.24</v>
       </c>
       <c r="O28" t="n">
-        <v>3.06</v>
+        <v>2.39</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="V28" t="n">
-        <v>8.699999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.98</v>
+        <v>5.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>4.7</v>
+        <v>6.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>3.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH5" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.53</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1501,13 +1501,13 @@
         <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.46</v>
@@ -1516,16 +1516,16 @@
         <v>2.78</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
         <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
@@ -1534,7 +1534,7 @@
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
         <v>2.08</v>
@@ -1543,10 +1543,10 @@
         <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
         <v>1.91</v>
@@ -1558,7 +1558,7 @@
         <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.81</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
         <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
@@ -1644,40 +1644,40 @@
         <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD10" t="n">
         <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.48</v>
+        <v>5.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.41</v>
+        <v>1.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.05</v>
+        <v>4.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="V12" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.91</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.53</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
         <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.08</v>
+        <v>4.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>3.24</v>
+        <v>1.65</v>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,70 +2444,70 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.31</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
         <v>1.7</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.41</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
         <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
         <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.95</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>2.43</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.39</v>
+        <v>3.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>3.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.43</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
         <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.92</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3405,13 +3405,13 @@
         <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.06</v>
+        <v>3.43</v>
       </c>
       <c r="R25" t="n">
         <v>1.43</v>
@@ -3420,7 +3420,7 @@
         <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
         <v>1.34</v>
@@ -3462,7 +3462,7 @@
         <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="P26" t="n">
         <v>2.05</v>
@@ -3539,13 +3539,13 @@
         <v>2.36</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="U26" t="n">
         <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
@@ -3560,28 +3560,28 @@
         <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
         <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
         <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>3.17</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
-        <v>3.06</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>2.74</v>
+        <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>8.699999999999999</v>
+        <v>4.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.98</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
-        <v>2.39</v>
+        <v>3.06</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.25</v>
+        <v>2.98</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N29" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="O29" t="n">
         <v>3.3</v>
@@ -3887,19 +3887,19 @@
         <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
         <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
         <v>6.5</v>
@@ -3923,7 +3923,7 @@
         <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AD29" t="n">
         <v>1.3</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>4.53</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.78</v>
+        <v>5.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -701,13 +701,13 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
         <v>2.42</v>
@@ -719,13 +719,13 @@
         <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46041.35416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.53</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="AB5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.5</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AA6" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1611,40 +1611,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="O10" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
         <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
         <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
         <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
@@ -1653,7 +1653,7 @@
         <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
         <v>2.14</v>
@@ -1671,7 +1671,7 @@
         <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
         <v>1.33</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.05</v>
+        <v>7.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.48</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.92</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.5</v>
+        <v>4.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>2.51</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>2.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3.25</v>
       </c>
       <c r="N20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.7</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="O21" t="n">
-        <v>2.43</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.72</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.74</v>
+        <v>4.16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.39</v>
+        <v>3.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>2.74</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>4.95</v>
+        <v>8.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>3.04</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.14</v>
+        <v>0.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>0.23</v>
       </c>
       <c r="N28" t="n">
-        <v>3.17</v>
+        <v>0.24</v>
       </c>
       <c r="O28" t="n">
-        <v>3.06</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>3.66</v>
       </c>
       <c r="T28" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>8.699999999999999</v>
+        <v>4.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.98</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>2.59</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.5</v>
+        <v>4.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2.51</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>2.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
         <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.48</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.58</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.51</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>5.36</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
         <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
         <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.6</v>
+        <v>3.88</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>4.16</v>
       </c>
       <c r="N21" t="n">
-        <v>1.87</v>
+        <v>3.41</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>4.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4.16</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>3.41</v>
+        <v>1.87</v>
       </c>
       <c r="O22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.3</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
         <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.92</v>
+        <v>4.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
         <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.75</v>
+        <v>3.92</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.52</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>3.48</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>2.74</v>
+        <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>8.6</v>
+        <v>4.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.04</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>4.95</v>
+        <v>8.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>3.04</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH5" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.53</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="AB6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1504,37 +1504,37 @@
         <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
         <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
         <v>2.08</v>
@@ -1543,22 +1543,22 @@
         <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
-        <v>3.19</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
         <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>4.12</v>
       </c>
       <c r="O11" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>3.19</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.51</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.14</v>
+        <v>3.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.5</v>
+        <v>4.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>2.51</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>2.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>7.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2099,31 +2099,31 @@
         <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
         <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.41</v>
@@ -2138,16 +2138,16 @@
         <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
         <v>1.36</v>
@@ -2215,7 +2215,7 @@
         <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
         <v>2.5</v>
@@ -2230,22 +2230,22 @@
         <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="U15" t="n">
         <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
         <v>3.5</v>
@@ -2260,19 +2260,19 @@
         <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
         <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.31</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>4.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.25</v>
       </c>
-      <c r="N19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AA19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.32</v>
       </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.03</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.88</v>
+        <v>4.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
@@ -2843,31 +2843,31 @@
         <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="M21" t="n">
-        <v>4.16</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.41</v>
+        <v>1.87</v>
       </c>
       <c r="O21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.3</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>4.16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.87</v>
+        <v>3.41</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>4.9</v>
+        <v>4.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.3</v>
       </c>
-      <c r="V23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
         <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3408,7 +3408,7 @@
         <v>3.52</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
         <v>3.4</v>
@@ -3420,19 +3420,19 @@
         <v>2.36</v>
       </c>
       <c r="T25" t="n">
-        <v>3.48</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
         <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
         <v>1.41</v>
@@ -3447,19 +3447,19 @@
         <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AD25" t="n">
         <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3524,13 +3524,13 @@
         <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -3542,22 +3542,22 @@
         <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA26" t="n">
         <v>1.95</v>
@@ -3566,19 +3566,19 @@
         <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>2.74</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>4.95</v>
+        <v>8.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>3.04</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.25</v>
       </c>
-      <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.45</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="M29" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
         <v>1.35</v>
@@ -3896,49 +3896,49 @@
         <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U29" t="n">
         <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
         <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC29" t="n">
         <v>2.94</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46041.71875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.53</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="AB5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.12</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="P11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V11" t="n">
         <v>4.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.14</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.94</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>4.12</v>
       </c>
       <c r="O12" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>3.19</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.51</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.14</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="AC15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.36</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>2.68</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.42</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.2</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>4.31</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
         <v>5.75</v>
@@ -683,10 +683,10 @@
         <v>3.18</v>
       </c>
       <c r="T2" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
         <v>5.15</v>
@@ -698,34 +698,34 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AD2" t="n">
         <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
         <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46041.35416666666</v>
@@ -906,40 +906,40 @@
         <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.71</v>
@@ -948,22 +948,22 @@
         <v>2.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46041.42013888889</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
         <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1040,13 +1040,13 @@
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1055,34 +1055,34 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
         <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
@@ -1156,7 +1156,7 @@
         <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
         <v>2.65</v>
@@ -1165,43 +1165,43 @@
         <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
         <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O9" t="n">
         <v>4.5</v>
@@ -1510,16 +1510,16 @@
         <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
         <v>7.4</v>
@@ -1528,37 +1528,37 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AA9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1620,31 +1620,31 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>5.39</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -1656,28 +1656,28 @@
         <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
         <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
         <v>7</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.35</v>
+        <v>3.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.51</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.14</v>
+        <v>3.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4.12</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
         <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>3.19</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.81</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>3.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>4.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>2.17</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.5</v>
+        <v>3.98</v>
       </c>
       <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.36</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>13.52</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2.68</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.45</v>
+        <v>2.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="M18" t="n">
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>2.91</v>
@@ -2581,16 +2581,16 @@
         <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
         <v>7.5</v>
@@ -2602,28 +2602,28 @@
         <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
         <v>1.32</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2801,19 +2801,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
         <v>4</v>
@@ -2825,7 +2825,7 @@
         <v>2.47</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
         <v>1.3</v>
@@ -2843,13 +2843,13 @@
         <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>4.31</v>
@@ -2858,16 +2858,16 @@
         <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
         <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
         <v>3.9</v>
@@ -2935,7 +2935,7 @@
         <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
@@ -2947,13 +2947,13 @@
         <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V21" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
@@ -2962,31 +2962,31 @@
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3039,34 +3039,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="P22" t="n">
         <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
         <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V22" t="n">
         <v>4.05</v>
@@ -3078,34 +3078,34 @@
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>6.62</v>
       </c>
       <c r="AA22" t="n">
         <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AC22" t="n">
         <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="T23" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>4.41</v>
       </c>
       <c r="O24" t="n">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.9</v>
+        <v>5.19</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.84</v>
       </c>
       <c r="AD24" t="n">
         <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,67 +3515,67 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
         <v>1.4</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.25</v>
       </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.45</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.39</v>
+        <v>3.06</v>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>3.12</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>3.04</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,43 +3872,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
         <v>2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
         <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U29" t="n">
         <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
@@ -3920,19 +3920,19 @@
         <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
         <v>1.74</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
         <v>1.35</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.72</v>
+        <v>5.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>5.75</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>2.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.39</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>5.39</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
         <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
         <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
         <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
         <v>7.1</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.25</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.17</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.61</v>
+        <v>2.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,67 +2444,67 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.42</v>
+        <v>4.31</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
@@ -2569,31 +2569,31 @@
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
         <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
@@ -2602,10 +2602,10 @@
         <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
         <v>2.2</v>
@@ -2617,16 +2617,16 @@
         <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
         <v>1.57</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,67 +3396,67 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
         <v>1.4</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,67 +3515,67 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
         <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AG26" t="n">
         <v>1.4</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.66</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>4.25</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>3.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.39</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
         <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.5</v>
+        <v>5.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
         <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.64</v>
+        <v>1.94</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>13.52</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.98</v>
+        <v>12.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>3.48</v>
+        <v>2.82</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>13.52</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.5</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.48</v>
       </c>
       <c r="T15" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.99</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.88</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.84</v>
       </c>
       <c r="AD23" t="n">
         <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="M24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.2</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.41</v>
-      </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.19</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T24" t="n">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
         <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,67 +3396,67 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
         <v>1.4</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,67 +3515,67 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.1</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3</v>
-      </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="U26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.4</v>
       </c>
-      <c r="V26" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.52</v>
+        <v>4.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
         <v>1.4</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>2.74</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.32</v>
+        <v>3.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O28" t="n">
         <v>2.3</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.06</v>
-      </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>3.66</v>
       </c>
       <c r="T28" t="n">
-        <v>3.12</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.04</v>
+        <v>5.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
         <v>2.15</v>
@@ -3893,16 +3893,16 @@
         <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="W29" t="n">
         <v>1.06</v>
@@ -3914,7 +3914,7 @@
         <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA29" t="n">
         <v>1.94</v>
@@ -3923,22 +3923,22 @@
         <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46041.71875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>5.75</v>
+        <v>2.72</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V5" t="n">
         <v>5</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>5.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1495,10 +1495,10 @@
         <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
         <v>4.5</v>
@@ -1507,22 +1507,22 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="T9" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="U9" t="n">
         <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
@@ -1534,13 +1534,13 @@
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
         <v>3.9</v>
@@ -1549,16 +1549,16 @@
         <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>3.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.54</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="P11" t="n">
-        <v>2.51</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>5.39</v>
       </c>
       <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.22</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
         <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.64</v>
+        <v>1.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.39</v>
+        <v>7.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
         <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.94</v>
+        <v>2.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="O16" t="n">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>2.77</v>
+        <v>2.97</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
         <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.35</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="U21" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>6.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.17</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z22" t="n">
-        <v>6.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4.41</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
         <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>2.7</v>
@@ -942,13 +942,13 @@
         <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD4" t="n">
         <v>1.32</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.72</v>
+        <v>5.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>5.75</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
         <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>5.26</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1513,7 +1513,7 @@
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
         <v>3.13</v>
@@ -1522,13 +1522,13 @@
         <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
         <v>1.35</v>
@@ -1537,10 +1537,10 @@
         <v>2.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
         <v>3.9</v>
@@ -1552,13 +1552,13 @@
         <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.66</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>4.25</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>3.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.39</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>5.39</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
         <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
         <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
@@ -2007,34 +2007,34 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG13" t="n">
         <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>13.52</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>1.62</v>
@@ -2108,19 +2108,19 @@
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -2132,16 +2132,16 @@
         <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>3.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
         <v>2.7</v>
@@ -2150,10 +2150,10 @@
         <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
@@ -2227,10 +2227,10 @@
         <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="U15" t="n">
         <v>1.28</v>
@@ -2242,22 +2242,22 @@
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
         <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1.18</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.03</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
         <v>1.85</v>
@@ -2626,10 +2626,10 @@
         <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>2.82</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>3.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
         <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.17</v>
       </c>
-      <c r="S21" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z21" t="n">
-        <v>6.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.5</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.35</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>6.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>3.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
         <v>2.6</v>
@@ -3408,13 +3408,13 @@
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
         <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>2.62</v>
@@ -3423,10 +3423,10 @@
         <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -3435,31 +3435,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>3.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="P26" t="n">
         <v>2.08</v>
@@ -3533,10 +3533,10 @@
         <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="T26" t="n">
         <v>3.44</v>
@@ -3545,7 +3545,7 @@
         <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
         <v>1.01</v>
@@ -3557,13 +3557,13 @@
         <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>4.25</v>
@@ -3572,7 +3572,7 @@
         <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
         <v>1.75</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>2.74</v>
+        <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.32</v>
+        <v>3.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="N29" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
         <v>3.3</v>
@@ -3887,19 +3887,19 @@
         <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
         <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
         <v>6.3</v>
@@ -3908,37 +3908,37 @@
         <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="AA29" t="n">
         <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46041.71875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
         <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
         <v>5.75</v>
@@ -689,7 +689,7 @@
         <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,25 +698,25 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
         <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -725,7 +725,7 @@
         <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46041.35416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>4.12</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>5.75</v>
+        <v>2.63</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
         <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
         <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="W11" t="n">
         <v>1.14</v>
@@ -1769,13 +1769,13 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
         <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB11" t="n">
         <v>2.6</v>
@@ -1787,16 +1787,16 @@
         <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AF11" t="n">
         <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.39</v>
+        <v>6.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
         <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AG12" t="n">
         <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
         <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.04</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,67 +2444,67 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>4.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
         <v>1.33</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
         <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
         <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.32</v>
+        <v>3.68</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.17</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z22" t="n">
-        <v>6.62</v>
+        <v>4.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3.16</v>
+        <v>2.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>3.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="P25" t="n">
         <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC25" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.01</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>3.17</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>4.95</v>
+        <v>8.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>3.04</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>0.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0.23</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>0.24</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>3.66</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46041.8125</v>
+        <v>46041.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.23</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="O6" t="n">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.42</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.3</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
         <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
         <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.04</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.36</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2364,34 +2364,34 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,37 +2682,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>4.36</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
@@ -2721,34 +2721,34 @@
         <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>3.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3.16</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
         <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="P26" t="n">
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AF26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC26" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -662,10 +662,10 @@
         <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.91</v>
@@ -704,7 +704,7 @@
         <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
         <v>2.2</v>
@@ -716,16 +716,16 @@
         <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46041.35416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.55</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.23</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
-        <v>4.9</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>3.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.3</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>1.58</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1867,16 +1867,16 @@
         <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
         <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>7.7</v>
@@ -1888,22 +1888,22 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
         <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
         <v>1.8</v>
@@ -1912,10 +1912,10 @@
         <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
         <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.04</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.92</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
         <v>4.6</v>
@@ -2343,10 +2343,10 @@
         <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="T16" t="n">
         <v>3.05</v>
@@ -2370,10 +2370,10 @@
         <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>3.68</v>
@@ -2388,7 +2388,7 @@
         <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
         <v>1.2</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.1</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.35</v>
-      </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
         <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
         <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>
@@ -2620,16 +2620,16 @@
         <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
         <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>3.17</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>8.6</v>
+        <v>4.95</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.04</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>4.95</v>
+        <v>8.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>3.04</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
@@ -942,22 +942,22 @@
         <v>3.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
         <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG4" t="n">
         <v>1.25</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.43</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.63</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.46</v>
+        <v>3.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.55</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1492,43 +1492,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
         <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
         <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
         <v>1.35</v>
@@ -1537,28 +1537,28 @@
         <v>2.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AF9" t="n">
         <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>3.88</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>7.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>8.09</v>
       </c>
       <c r="R10" t="n">
         <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
         <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>3.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>2.03</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
         <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.44</v>
       </c>
       <c r="U14" t="n">
         <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
@@ -2132,10 +2132,10 @@
         <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
         <v>4.3</v>
@@ -2144,7 +2144,7 @@
         <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
         <v>1.8</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
@@ -2462,10 +2462,10 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="T17" t="n">
         <v>2.99</v>
@@ -2489,10 +2489,10 @@
         <v>3.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
         <v>3.8</v>
@@ -2501,13 +2501,13 @@
         <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
         <v>1.65</v>
@@ -2566,10 +2566,10 @@
         <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
         <v>2.91</v>
@@ -2581,13 +2581,13 @@
         <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
         <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
         <v>1.31</v>
@@ -2596,7 +2596,7 @@
         <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.08</v>
@@ -2611,7 +2611,7 @@
         <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
         <v>4</v>
@@ -2620,7 +2620,7 @@
         <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
         <v>1.85</v>
@@ -2801,19 +2801,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
         <v>3.9</v>
@@ -2822,10 +2822,10 @@
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
         <v>1.28</v>
@@ -2837,34 +2837,34 @@
         <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
         <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
         <v>1.7</v>
@@ -2920,16 +2920,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="O21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
@@ -2941,13 +2941,13 @@
         <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V21" t="n">
         <v>4.05</v>
@@ -2962,13 +2962,13 @@
         <v>1.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="AA21" t="n">
         <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC21" t="n">
         <v>1.9</v>
@@ -2983,10 +2983,10 @@
         <v>3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3039,19 +3039,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>4.22</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q22" t="n">
         <v>2.33</v>
@@ -3063,16 +3063,16 @@
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
         <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
@@ -3084,13 +3084,13 @@
         <v>4.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD22" t="n">
         <v>1.53</v>
@@ -3102,10 +3102,10 @@
         <v>2.45</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.16</v>
+        <v>2.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O25" t="n">
         <v>3.05</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3</v>
-      </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R25" t="n">
         <v>1.43</v>
@@ -3438,16 +3438,16 @@
         <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="AD25" t="n">
         <v>1.22</v>
@@ -3459,7 +3459,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
         <v>2.08</v>
@@ -3533,13 +3533,13 @@
         <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="U26" t="n">
         <v>1.28</v>
@@ -3551,7 +3551,7 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
         <v>1.4</v>
@@ -3560,13 +3560,13 @@
         <v>2.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD26" t="n">
         <v>1.18</v>
@@ -3578,10 +3578,10 @@
         <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="P27" t="n">
         <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="R27" t="n">
         <v>1.26</v>
@@ -3661,7 +3661,7 @@
         <v>2.29</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V27" t="n">
         <v>4.95</v>
@@ -3670,25 +3670,25 @@
         <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
         <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
         <v>1.44</v>
@@ -3697,10 +3697,10 @@
         <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>2.94</v>
@@ -3771,43 +3771,43 @@
         <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U28" t="n">
         <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
         <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
         <v>3.04</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AB28" t="n">
         <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
         <v>1.8</v>
@@ -3875,10 +3875,10 @@
         <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O29" t="n">
         <v>3.3</v>
@@ -3887,46 +3887,46 @@
         <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
         <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.06</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.78</v>
+        <v>3.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE29" t="n">
         <v>1.73</v>
@@ -3935,10 +3935,10 @@
         <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46041.71875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -683,13 +683,13 @@
         <v>3.18</v>
       </c>
       <c r="T2" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,13 +698,13 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
         <v>2.2</v>
@@ -716,13 +716,13 @@
         <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
         <v>2.5</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
@@ -936,13 +936,13 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB4" t="n">
         <v>1.92</v>
@@ -951,7 +951,7 @@
         <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
         <v>1.58</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
         <v>5</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.43</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.63</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.46</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.09</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N12" t="n">
-        <v>6.25</v>
+        <v>7.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.29</v>
+        <v>1.54</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.76</v>
+        <v>6.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V13" t="n">
         <v>4.5</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.3</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>2.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.88</v>
+        <v>2.86</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>2.93</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>9.199999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>2.93</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.7</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.04</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.7</v>
+        <v>4.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
         <v>4.6</v>
@@ -2343,10 +2343,10 @@
         <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
         <v>3.05</v>
@@ -2358,10 +2358,10 @@
         <v>8.5</v>
       </c>
       <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.38</v>
@@ -2373,7 +2373,7 @@
         <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
         <v>3.68</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
         <v>2.5</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.3</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.17</v>
       </c>
-      <c r="S21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Z21" t="n">
-        <v>6.65</v>
+        <v>4.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>4.16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>4.22</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
       <c r="O23" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="P24" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
         <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
         <v>1.26</v>
@@ -3658,10 +3658,10 @@
         <v>3.66</v>
       </c>
       <c r="T27" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
         <v>4.95</v>
@@ -3679,19 +3679,19 @@
         <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
         <v>1.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AF27" t="n">
         <v>2.5</v>
@@ -3700,7 +3700,7 @@
         <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
         <v>3.4</v>
@@ -3762,22 +3762,22 @@
         <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
         <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>3.12</v>
+        <v>3.21</v>
       </c>
       <c r="U28" t="n">
         <v>1.36</v>
@@ -3789,25 +3789,25 @@
         <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
         <v>1.8</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N29" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
         <v>3.3</v>
@@ -3890,49 +3890,49 @@
         <v>2.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
         <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
         <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
         <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
         <v>1.32</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.76</v>
+        <v>6.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V11" t="n">
         <v>4.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.3</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.54</v>
+        <v>2.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.88</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.02</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.86</v>
+        <v>1.89</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.93</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2.7</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.04</v>
+        <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
-        <v>2.93</v>
+        <v>5.5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>9.199999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.54</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
         <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
         <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>4.54</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AD20" t="n">
         <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.27</v>
+        <v>2.66</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="M26" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="O26" t="n">
         <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="T26" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
         <v>8</v>
       </c>
       <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.01</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.25</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.76</v>
+        <v>6.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V10" t="n">
         <v>4.5</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.3</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.54</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>2.86</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N11" t="n">
-        <v>6.25</v>
+        <v>7.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.29</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.88</v>
+        <v>3.22</v>
       </c>
       <c r="N12" t="n">
-        <v>7.15</v>
+        <v>3.76</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.09</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="M14" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>3.1</v>
@@ -2102,13 +2102,13 @@
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T14" t="n">
         <v>3.4</v>
@@ -2117,7 +2117,7 @@
         <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -2126,19 +2126,19 @@
         <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD14" t="n">
         <v>1.18</v>
@@ -2147,7 +2147,7 @@
         <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
         <v>1.36</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
         <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>4.54</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AD18" t="n">
         <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.54</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.85</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="M22" t="n">
-        <v>4.16</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.3</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.88</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>10</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="M25" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="O25" t="n">
         <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="T25" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="S26" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
         <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3762,25 +3762,25 @@
         <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="T28" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
         <v>7</v>
@@ -3789,37 +3789,37 @@
         <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>3.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
         <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="M29" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
         <v>2.5</v>
@@ -3908,7 +3908,7 @@
         <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
@@ -3917,25 +3917,25 @@
         <v>3.38</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC29" t="n">
         <v>3.25</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
         <v>1.44</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
         <v>5</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.25</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1516,22 +1516,22 @@
         <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
         <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
         <v>2.89</v>
@@ -1552,10 +1552,10 @@
         <v>2.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
         <v>1.2</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="N10" t="n">
-        <v>6.25</v>
+        <v>7.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.29</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.88</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>7.15</v>
+        <v>3.76</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.09</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.02</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.89</v>
+        <v>2.86</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.57</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>2.57</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>13</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>4.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.54</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>3.74</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="AD18" t="n">
         <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
         <v>1.85</v>
@@ -2864,10 +2864,10 @@
         <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.24</v>
       </c>
-      <c r="V24" t="n">
-        <v>10</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
@@ -921,10 +921,10 @@
         <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
         <v>6.35</v>
@@ -939,13 +939,13 @@
         <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
         <v>2.88</v>
@@ -954,10 +954,10 @@
         <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
         <v>1.25</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.25</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
         <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.43</v>
@@ -1537,10 +1537,10 @@
         <v>2.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
         <v>3.72</v>
@@ -1549,13 +1549,13 @@
         <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="n">
         <v>1.2</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.88</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>7.15</v>
+        <v>3.76</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.09</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD10" t="n">
         <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.76</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>8.09</v>
       </c>
       <c r="R11" t="n">
         <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="U11" t="n">
         <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>2.09</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.02</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.89</v>
+        <v>2.86</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.02</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.86</v>
+        <v>1.89</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2102,7 +2102,7 @@
         <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
@@ -2114,7 +2114,7 @@
         <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
         <v>6.75</v>
@@ -2144,10 +2144,10 @@
         <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG14" t="n">
         <v>1.14</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
         <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
@@ -2224,10 +2224,10 @@
         <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="T15" t="n">
         <v>3.4</v>
@@ -2251,10 +2251,10 @@
         <v>2.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>4.33</v>
@@ -2266,7 +2266,7 @@
         <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
         <v>1.36</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.54</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
         <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AF23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.24</v>
       </c>
-      <c r="V23" t="n">
-        <v>10</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>3.1</v>
@@ -3429,22 +3429,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
         <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
         <v>3.72</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -3536,10 +3536,10 @@
         <v>1.63</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="U26" t="n">
         <v>1.28</v>
@@ -3560,16 +3560,16 @@
         <v>2.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>4.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE26" t="n">
         <v>1.95</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.66</v>
+        <v>2.67</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>3.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O28" t="n">
         <v>2.3</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>2.67</v>
+        <v>3.66</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>4.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.13</v>
+        <v>5.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.84</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
         <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O29" t="n">
         <v>3.3</v>
@@ -3896,28 +3896,28 @@
         <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="W29" t="n">
         <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
         <v>1.85</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="P2" t="n">
         <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,10 +698,10 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.54</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>2.58</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.25</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.02</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1382,46 +1382,46 @@
         <v>13.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
         <v>2.07</v>
@@ -1430,16 +1430,16 @@
         <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46041.53125</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.41</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q11" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" t="n">
-        <v>6.25</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.45</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.86</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.91</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>9.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.03</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
         <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="S25" t="n">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC25" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z26" t="n">
         <v>3</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -689,7 +689,7 @@
         <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,7 +698,7 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
         <v>4.4</v>
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
         <v>2.5</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
@@ -1138,7 +1138,7 @@
         <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
@@ -1159,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
         <v>1.43</v>
@@ -1171,10 +1171,10 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
         <v>3.7</v>
@@ -1183,7 +1183,7 @@
         <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>3.1</v>
@@ -1192,13 +1192,13 @@
         <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
         <v>2.3</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>8.09</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
         <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1733,13 +1733,13 @@
         <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="N11" t="n">
-        <v>6.25</v>
+        <v>6.84</v>
       </c>
       <c r="O11" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="P11" t="n">
         <v>2.62</v>
@@ -1748,19 +1748,19 @@
         <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W11" t="n">
         <v>1.18</v>
@@ -1772,31 +1772,31 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
         <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.09</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U12" t="n">
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2920,34 +2920,34 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
         <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
         <v>4.05</v>
@@ -2959,7 +2959,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
         <v>6.5</v>
@@ -2968,22 +2968,22 @@
         <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
         <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
         <v>1.8</v>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="N22" t="n">
         <v>1.85</v>
@@ -3063,19 +3063,19 @@
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
         <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.17</v>
@@ -3084,7 +3084,7 @@
         <v>4.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AB22" t="n">
         <v>2.3</v>
@@ -3102,10 +3102,10 @@
         <v>2.45</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
         <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
         <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="T25" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="S26" t="n">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AF26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC26" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O27" t="n">
         <v>2.3</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.13</v>
+        <v>5.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.84</v>
+        <v>2.32</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -906,37 +906,37 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
         <v>3.7</v>
@@ -951,19 +951,19 @@
         <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46041.42013888889</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="N8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
         <v>1.57</v>
@@ -1397,7 +1397,7 @@
         <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="U8" t="n">
         <v>1.5</v>
@@ -1409,16 +1409,16 @@
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
         <v>2.2</v>
@@ -1430,7 +1430,7 @@
         <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
         <v>1.6</v>
@@ -1439,7 +1439,7 @@
         <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46041.53125</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="N10" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8.09</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2.92</v>
+        <v>5.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.36</v>
       </c>
-      <c r="M11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="Z11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.85</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.76</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>8.16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
         <v>2.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>5.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>12.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>9.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>2.93</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.91</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>1.56</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,58 +2444,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1.22</v>
@@ -2507,10 +2507,10 @@
         <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3167,19 +3167,19 @@
         <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
         <v>3.04</v>
@@ -3200,7 +3200,7 @@
         <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
         <v>2.03</v>
@@ -3221,10 +3221,10 @@
         <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -3292,7 +3292,7 @@
         <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.05</v>
+        <v>3.69</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -3304,28 +3304,28 @@
         <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC24" t="n">
         <v>4.8</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="S25" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="T26" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.01</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="N2" t="n">
         <v>6.16</v>
@@ -671,7 +671,7 @@
         <v>1.93</v>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
         <v>5.75</v>
@@ -686,10 +686,10 @@
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46041.42013888889</v>
@@ -1016,64 +1016,64 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
         <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AF5" t="n">
         <v>2.4</v>
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
         <v>6</v>
@@ -1177,28 +1177,28 @@
         <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
         <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
         <v>2.3</v>
@@ -1373,43 +1373,43 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="M8" t="n">
-        <v>5.1</v>
+        <v>6.33</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>10.94</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
@@ -1418,28 +1418,28 @@
         <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46041.53125</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>4.46</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
         <v>5</v>
@@ -1507,19 +1507,19 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
         <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
         <v>7.2</v>
@@ -1537,25 +1537,25 @@
         <v>2.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AD9" t="n">
         <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
         <v>1.2</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.36</v>
       </c>
-      <c r="M10" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>3.76</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>8.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
         <v>2.95</v>
       </c>
       <c r="U11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.33</v>
       </c>
-      <c r="V11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
         <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8.16</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.08</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>4.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>12.3</v>
+        <v>3.22</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.9</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="S14" t="n">
-        <v>2.82</v>
+        <v>2.35</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>12.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>9.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.91</v>
+        <v>2.93</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>4.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="Z16" t="n">
         <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
         <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.69</v>
       </c>
       <c r="O17" t="n">
         <v>2.5</v>
@@ -2462,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
         <v>2.75</v>
@@ -2474,13 +2474,13 @@
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
         <v>1.35</v>
@@ -2489,7 +2489,7 @@
         <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB17" t="n">
         <v>1.67</v>
@@ -2507,7 +2507,7 @@
         <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
         <v>1.73</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.88</v>
-      </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
         <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.54</v>
+        <v>3.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O20" t="n">
         <v>4.6</v>
@@ -2843,7 +2843,7 @@
         <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AA20" t="n">
         <v>2.15</v>
@@ -2855,7 +2855,7 @@
         <v>3.58</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
         <v>1.95</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="O21" t="n">
         <v>2.15</v>
@@ -2944,7 +2944,7 @@
         <v>4.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
         <v>1.88</v>
@@ -2959,7 +2959,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
         <v>6.5</v>
@@ -2983,10 +2983,10 @@
         <v>3.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3039,67 +3039,67 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>4.01</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
         <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AG22" t="n">
         <v>1.85</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="O23" t="n">
         <v>2.3</v>
@@ -3176,10 +3176,10 @@
         <v>5.09</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
         <v>3.04</v>
@@ -3188,7 +3188,7 @@
         <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
@@ -3203,7 +3203,7 @@
         <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
         <v>1.7</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
         <v>3.2</v>
@@ -3289,16 +3289,16 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
         <v>3.5</v>
@@ -3325,19 +3325,19 @@
         <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG24" t="n">
         <v>1.36</v>
@@ -3402,7 +3402,7 @@
         <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -3411,31 +3411,31 @@
         <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
         <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
         <v>2.7</v>
@@ -3444,19 +3444,19 @@
         <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD25" t="n">
         <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>1.4</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>2.9</v>
@@ -3560,10 +3560,10 @@
         <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>3.77</v>
@@ -3634,67 +3634,67 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
         <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="U27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V27" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
         <v>1.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
         <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AG27" t="n">
         <v>1.29</v>
@@ -3756,55 +3756,55 @@
         <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
         <v>3.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
         <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
         <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
         <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AD28" t="n">
         <v>1.21</v>
@@ -3819,7 +3819,7 @@
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,34 +3872,34 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="O29" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.42</v>
       </c>
       <c r="V29" t="n">
         <v>6.35</v>
@@ -3923,7 +3923,7 @@
         <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AD29" t="n">
         <v>1.3</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>4.48</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.44</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>8.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
         <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.16</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
         <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>4.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="N13" t="n">
-        <v>4.01</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>3.88</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>1.16</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.22</v>
+        <v>17.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>12.3</v>
+        <v>3.22</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.9</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.82</v>
+        <v>2.35</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>3.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.76</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.75</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>4.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
         <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="T25" t="n">
         <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
         <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46041.41666666666</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
         <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1510,52 +1510,52 @@
         <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
         <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
         <v>1.2</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.16</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>4.01</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
         <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.01</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
         <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.88</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2.7</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.23</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="M19" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
         <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>2.61</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,46 +2801,46 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.76</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
         <v>2.8</v>
@@ -2849,25 +2849,25 @@
         <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
         <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
         <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.41</v>
+        <v>1.84</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>4.01</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.15</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.6</v>
       </c>
-      <c r="N22" t="n">
+      <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.84</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>4.28</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O24" t="n">
         <v>2.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
       <c r="P24" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
         <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="M26" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
         <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
         <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>1.95</v>
@@ -817,10 +817,10 @@
         <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA3" t="n">
         <v>2.62</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6.5</v>
+        <v>4.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.22</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>4.01</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>8.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="U11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.33</v>
       </c>
-      <c r="V11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
         <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="P12" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>3.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.16</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
         <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH13" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
@@ -2111,13 +2111,13 @@
         <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
@@ -2126,31 +2126,31 @@
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AH14" t="n">
         <v>4.2</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.01</v>
+        <v>3.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.69</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>1.73</v>
-      </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
         <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.6</v>
       </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.84</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.41</v>
+        <v>1.84</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>4.01</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.15</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O23" t="n">
         <v>2.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="P24" t="n">
         <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.07</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>2.58</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
         <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
         <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
         <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3753,40 +3753,40 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="O28" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
         <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
         <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.07</v>
@@ -3807,19 +3807,19 @@
         <v>3.76</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
         <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="O29" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P29" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
         <v>2.73</v>
@@ -3902,7 +3902,7 @@
         <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="W29" t="n">
         <v>1.06</v>
@@ -3911,31 +3911,31 @@
         <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
         <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AD29" t="n">
         <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
         <v>1.44</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46041.79166666666</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="U4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
@@ -936,19 +936,19 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
         <v>4.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
         <v>1.42</v>
@@ -957,13 +957,13 @@
         <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46041.42013888889</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.44</v>
       </c>
-      <c r="M5" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>4.48</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>6.33</v>
+        <v>5.1</v>
       </c>
       <c r="N8" t="n">
-        <v>10.94</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.859999999999999</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
@@ -1403,37 +1403,37 @@
         <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="W8" t="n">
         <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
         <v>1.18</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.01</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.33</v>
       </c>
-      <c r="V10" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
         <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.16</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>4.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
@@ -2245,16 +2245,16 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>4.4</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
         <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
         <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD16" t="n">
         <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.88</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
         <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.95</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>3.05</v>
@@ -3316,13 +3316,13 @@
         <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
         <v>1.53</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
         <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.84</v>
+        <v>2.43</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>2.58</v>
       </c>
       <c r="O26" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
         <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -787,19 +787,19 @@
         <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="T3" t="n">
         <v>3.58</v>
@@ -808,13 +808,13 @@
         <v>1.21</v>
       </c>
       <c r="V3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
         <v>1.5</v>
@@ -823,22 +823,22 @@
         <v>2.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
         <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AG3" t="n">
         <v>1.4</v>
@@ -906,40 +906,40 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T4" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
         <v>1.8</v>
@@ -948,19 +948,19 @@
         <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
         <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
         <v>1.57</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>4.48</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.44</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1412,10 +1412,10 @@
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
         <v>1.6</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1519,16 +1519,16 @@
         <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
         <v>7.2</v>
       </c>
       <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.36</v>
@@ -1537,25 +1537,25 @@
         <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="AD9" t="n">
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
         <v>1.2</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,70 +1611,70 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="N10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.17</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
         <v>2.75</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>5.15</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.01</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>4.01</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="P13" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.28</v>
       </c>
-      <c r="V15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2325,25 +2325,25 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>2.88</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
         <v>2.6</v>
@@ -2352,10 +2352,10 @@
         <v>3.22</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2364,22 +2364,22 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
         <v>1.91</v>
@@ -2388,10 +2388,10 @@
         <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
         <v>1.85</v>
@@ -2626,10 +2626,10 @@
         <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,61 +2682,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
         <v>1.85</v>
@@ -2745,10 +2745,10 @@
         <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.41</v>
+        <v>1.84</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>4.01</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.15</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.6</v>
       </c>
-      <c r="N22" t="n">
+      <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.84</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="N23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4.2</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.07</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
         <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="U24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.29</v>
       </c>
-      <c r="V24" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="T25" t="n">
-        <v>3.38</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.43</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.86</v>
+        <v>0.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>0.23</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>0.24</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,70 +3872,70 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.69</v>
       </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.73</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AC29" t="n">
         <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF29" t="n">
         <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
         <v>1.44</v>
@@ -4054,7 +4054,7 @@
         <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AH30" t="n">
         <v>1.29</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.44</v>
       </c>
-      <c r="M5" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>4.48</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,70 +1611,70 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>5.15</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.22</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.6</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
         <v>2.75</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="N12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7.5</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.08</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.74</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
         <v>2.75</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
         <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC16" t="n">
         <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.35</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="T17" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
         <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.1</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.29</v>
       </c>
-      <c r="V23" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4.2</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.75</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.07</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,70 +3396,70 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC25" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="T26" t="n">
-        <v>3.38</v>
+        <v>2.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.52</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>0.23</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>0.24</v>
+        <v>3.28</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.22</v>
+        <v>3.76</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.22</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.76</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4060,7 +4060,7 @@
         <v>1.29</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46041.79166666666</v>
+        <v>46041.8125</v>
       </c>
     </row>
     <row r="31">

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -659,31 +659,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>6.16</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
         <v>1.5</v>
@@ -701,31 +701,31 @@
         <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
         <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC2" t="n">
         <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46041.35416666666</v>
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.75</v>
+        <v>5.03</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R3" t="n">
         <v>1.67</v>
@@ -802,28 +802,28 @@
         <v>2.05</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
         <v>2.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AB3" t="n">
         <v>1.4</v>
@@ -832,19 +832,19 @@
         <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46041.41666666666</v>
@@ -903,67 +903,67 @@
         <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.66</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
         <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46041.42013888889</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="M5" t="n">
         <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="W5" t="n">
         <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1.52</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="M8" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="Q8" t="n">
         <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
         <v>4.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
         <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
         <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46041.53125</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,70 +1611,70 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="N10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.74</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
         <v>2.75</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>4.01</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="P11" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
         <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>5.15</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.01</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.14</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="T14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>3.25</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>10</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AG15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>2.02</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.74</v>
+        <v>4.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
         <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.35</v>
+        <v>3.84</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
         <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.95</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2920,19 +2920,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="O21" t="n">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>2.2</v>
@@ -2941,49 +2941,49 @@
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.54</v>
+        <v>2.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
         <v>1.25</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="P22" t="n">
         <v>2.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -3063,49 +3063,49 @@
         <v>4.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="V22" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z22" t="n">
         <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.83</v>
+        <v>3.54</v>
       </c>
       <c r="T27" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>4.85</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.19</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.76</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.52</v>
+        <v>2.22</v>
       </c>
       <c r="M28" t="n">
-        <v>0.23</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>0.24</v>
+        <v>3.28</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.22</v>
+        <v>3.76</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.48</v>
+        <v>4.32</v>
       </c>
       <c r="N6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1153,16 +1153,16 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
         <v>6</v>
@@ -1171,37 +1171,37 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
         <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46041.45833333334</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.3</v>
+        <v>4.61</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1519,10 +1519,10 @@
         <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
@@ -1537,28 +1537,28 @@
         <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.79</v>
+        <v>3.54</v>
       </c>
       <c r="AD9" t="n">
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46041.54166666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.22</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="N11" t="n">
-        <v>4.01</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>3.74</v>
+        <v>4.86</v>
       </c>
       <c r="N12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V12" t="n">
         <v>4.6</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>2.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.11</v>
+        <v>2.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1968,34 +1968,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="O13" t="n">
         <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
         <v>7.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>7.2</v>
@@ -2007,22 +2007,22 @@
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>2.2</v>
@@ -2034,7 +2034,7 @@
         <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>1.62</v>
@@ -2132,10 +2132,10 @@
         <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
         <v>2.97</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="N15" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
@@ -2224,10 +2224,10 @@
         <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
         <v>3.25</v>
@@ -2236,43 +2236,43 @@
         <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
         <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
         <v>1.96</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
         <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>2.5</v>
@@ -2370,7 +2370,7 @@
         <v>2.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB16" t="n">
         <v>1.67</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="U17" t="n">
         <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z17" t="n">
         <v>2.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
         <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>2.91</v>
@@ -2608,10 +2608,10 @@
         <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>3.84</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.86</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V21" t="n">
         <v>3.85</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.45</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="O22" t="n">
-        <v>2.35</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.15</v>
+        <v>3.52</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4.2</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.3</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
         <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U24" t="n">
         <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
         <v>1.18</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3396,61 +3396,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="P25" t="n">
         <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T25" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
         <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
         <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
         <v>4.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
         <v>1.95</v>
@@ -3462,7 +3462,7 @@
         <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
         <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
         <v>2.88</v>
@@ -3545,13 +3545,13 @@
         <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.34</v>
@@ -3560,25 +3560,25 @@
         <v>2.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3753,31 +3753,31 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U28" t="n">
         <v>1.35</v>
@@ -3789,37 +3789,37 @@
         <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
         <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
         <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
         <v>2.2</v>
@@ -3890,49 +3890,49 @@
         <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T29" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W29" t="n">
         <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
         <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AG29" t="n">
         <v>1.33</v>
@@ -4003,37 +4003,37 @@
         <v>3.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.75</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.83</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA30" t="n">
         <v>1.95</v>
@@ -4045,19 +4045,19 @@
         <v>3.34</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG30" t="n">
         <v>1.58</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46041.8125</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
         <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="T8" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
         <v>4.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB8" t="n">
         <v>2.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46041.53125</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.61</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>5.36</v>
+        <v>5.63</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -1516,7 +1516,7 @@
         <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U9" t="n">
         <v>1.33</v>
@@ -1537,22 +1537,22 @@
         <v>2.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB9" t="n">
         <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
         <v>1.29</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>7.3</v>
@@ -1647,37 +1647,37 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="T11" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
         <v>2.7</v>
@@ -1867,25 +1867,25 @@
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="W12" t="n">
         <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
         <v>1.13</v>
@@ -1894,28 +1894,28 @@
         <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AD12" t="n">
         <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1971,46 +1971,46 @@
         <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>6.75</v>
+        <v>7.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
         <v>7.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
         <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
         <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
         <v>1.95</v>
@@ -2019,7 +2019,7 @@
         <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
@@ -2031,10 +2031,10 @@
         <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2206,64 +2206,64 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
         <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
         <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
         <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
         <v>1.8</v>
@@ -2272,7 +2272,7 @@
         <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>4.33</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>5.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>2.41</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N19" t="n">
-        <v>3.59</v>
+        <v>3.69</v>
       </c>
       <c r="O19" t="n">
         <v>2.88</v>
@@ -2700,55 +2700,55 @@
         <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="M21" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="O21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.35</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.86</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
         <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>2.61</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46041.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="R24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.44</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z24" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46041.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="M25" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="T25" t="n">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46041.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="T26" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V26" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.88</v>
+        <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
         <v>2.35</v>
@@ -3649,28 +3649,28 @@
         <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="T27" t="n">
         <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="W27" t="n">
         <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
         <v>1.14</v>
@@ -3679,10 +3679,10 @@
         <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC27" t="n">
         <v>2.2</v>
@@ -3691,7 +3691,7 @@
         <v>1.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AF27" t="n">
         <v>2.5</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N28" t="n">
         <v>3.25</v>
@@ -3765,61 +3765,61 @@
         <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
         <v>4.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
         <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
         <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
         <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>6.2</v>
+        <v>5.85</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
         <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46041.71875</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1356,20 +1356,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,19 +1585,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4.25</v>
+        <v>7.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.36</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1704,16 +1704,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>6.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.83</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>7.3</v>
+        <v>4.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>2.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1823,99 +1823,99 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.33</v>
       </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="V12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.78</v>
+        <v>1.86</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,99 +1942,99 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>7.9</v>
+        <v>4.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2083,77 +2083,77 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>2.82</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>3.37</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.91</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
         <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.97</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,99 +2180,99 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>1.17</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>15.03</v>
       </c>
       <c r="O15" t="n">
-        <v>3.37</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.38</v>
+        <v>3.26</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46041.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.95</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.33</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>5.1</v>
+        <v>2.91</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.41</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="W18" t="n">
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.35</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.86</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>3.35</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>1.86</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.85</v>
+        <v>2.41</v>
       </c>
       <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.15</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46041.66666666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="M28" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>3.62</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.15</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AF28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.71</v>
+        <v>3.18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W30" t="n">
         <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46041.8125</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46041.89583333334</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,63 +2299,63 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
         <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2364,34 +2364,34 @@
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.33</v>
+        <v>2.19</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>5.1</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.41</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,99 +2775,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.95</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46041.625</v>
@@ -2903,20 +2903,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3022,20 +3022,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>3.62</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.15</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AF27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46041.70833333334</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.18</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="U30" t="n">
         <v>1.31</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46041.8125</v>
@@ -4113,10 +4113,10 @@
         <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O31" t="n">
         <v>2.8</v>
@@ -4128,49 +4128,49 @@
         <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
         <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG31" t="n">
         <v>1.33</v>

--- a/jogos_2026-01-19.xlsx
+++ b/jogos_2026-01-19.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,22 +1585,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="T10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.85</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AB10" t="n">
         <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.59</v>
+        <v>3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,25 +1823,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>7.3</v>
@@ -1885,37 +1885,37 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46041.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,25 +1942,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4.25</v>
+        <v>7.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.36</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46041.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,99 +2299,99 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.17</v>
+        <v>1.78</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46041.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46041.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46041.625</v>
@@ -3144,17 +3144,17 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,96 +3370,96 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.46</v>
+        <v>3.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S25" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.88</v>
+        <v>5.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AH25" t="n">
         <v>1.44</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,19 +3489,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3511,74 +3511,74 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
       <c r="M26" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="T26" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
         <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.3</v>
+        <v>3.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AH26" t="n">
         <v>1.44</v>
@@ -3617,20 +3617,20 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3736,20 +3736,20 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3858,17 +3858,17 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3974,20 +3974,20 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -4060,7 +4060,7 @@
         <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46041.8125</v>
+        <v>46041.79166666666</v>
       </c>
     </row>
     <row r="31">
